--- a/Output/Table_S1_comp_rep.xlsx
+++ b/Output/Table_S1_comp_rep.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinbulla/Dropbox/Science/MS/I4R_Nat_Hum_Beh/Data/MaPe/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/martinbulla/Dropbox/Science/MS/I4R_Nat_Hum_Beh/Output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A17243-EF73-EE4C-AA6D-76BA7B761EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA0D1A1A-3B3D-0F4E-B282-D97FFEB5BE25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="460" windowWidth="28800" windowHeight="17540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="40960" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="List1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="73">
   <si>
     <t>ID</t>
   </si>
@@ -46,9 +46,6 @@
   </si>
   <si>
     <t>Note</t>
-  </si>
-  <si>
-    <t>Sampling density and biodiversity coldspots We found differences in sampling across HOLC grades. A total of 8% of HOLC A neighbourhoods did not display any bird records compared with 13% for grade-D polygons.</t>
   </si>
   <si>
     <t>05_paper_1_analyses_R4</t>
@@ -134,9 +131,6 @@
     <t>No</t>
   </si>
   <si>
-    <t>Table S2 is not showing this</t>
-  </si>
-  <si>
     <t>Sampling density was greatest in formerly A-graded neighbourhoods. Sampling density odds are 37% lower in B-graded neighbourhoods (OR: 0.63; 95% CI: 0.54, 0.73; P &lt; 0.001); 63% lower in C-graded neighbourhoods (OR: 0.37; 95% CI: 0.31, 0.43; P &lt; 0.001) and 74% lower in D-graded neighbourhoods (OR: 0.26; 95% CI: 0.21, 0.31; P &lt; 0.001) (Fig. 3).</t>
   </si>
   <si>
@@ -179,9 +173,6 @@
     <t>1074-1035</t>
   </si>
   <si>
-    <t>model coeficcients differs a bit</t>
-  </si>
-  <si>
     <t>Our generalized additive model revealed that year and HOLC grade were both significant predictors in explaining the cumulative sampling of bird biodiversity through time (P &lt; 0.001; Supplementary Table 4).</t>
   </si>
   <si>
@@ -215,9 +206,6 @@
     <t>Partially</t>
   </si>
   <si>
-    <t>Hold grade "B" bar is smaller than "A" for iNaturalist</t>
-  </si>
-  <si>
     <t xml:space="preserve">The ratio of sampling density between HOLC A and D grades was 2.021 in the year 2000 and grew to 2.74 by 2020, </t>
   </si>
   <si>
@@ -231,9 +219,6 @@
   </si>
   <si>
     <t xml:space="preserve">The most common citizen-science platforms, eBird and iNaturalist, appear to express different biases in sampling density, with eBird being more unevenly distributed, having more observations in HOLC A and B than in HOLC C and D grades (Fig. 3 and Supplementary Fig. 2). While iNaturalist data were much more evenly distributed across HOLC grades, it constitutes only a small fraction of the data (~1%) compared with eBird (Supplementary Fig. 2). </t>
-  </si>
-  <si>
-    <t>Fig. S2, Fig. 3, 2</t>
   </si>
   <si>
     <t>see above</t>
@@ -252,6 +237,36 @@
   </si>
   <si>
     <t>639-647</t>
+  </si>
+  <si>
+    <t>coefficients are slightly different from those in Table 1</t>
+  </si>
+  <si>
+    <t>We found differences in sampling across HOLC grades. A total of 8% of HOLC A neighbourhoods did not display any bird records compared with 13% for grade-D polygons.</t>
+  </si>
+  <si>
+    <t>Model coeficcients differs a bit</t>
+  </si>
+  <si>
+    <t>Was tough to reproduce as the model description did not match the script and the underlying data were accidentally multiplied.</t>
+  </si>
+  <si>
+    <t>Table S2 is not showing this; table  content does not reflect the one described in the table legend,  the single panel that we could reproduce was mislabled as log(sampling density) whereas sampling density was  shown.</t>
+  </si>
+  <si>
+    <t>Fig. 3, Table 1</t>
+  </si>
+  <si>
+    <t>No script.</t>
+  </si>
+  <si>
+    <t>Fig. S2, Fig. 3</t>
+  </si>
+  <si>
+    <t>In our reproduction the HOLC grade "B" bar is smaller than "A" for iNaturalist</t>
+  </si>
+  <si>
+    <t>In our reproduction the HOLC grade "B" bar is smaller than "A" for iNaturalist. Note that the authors reference Fig. 2, but the content is in Fig. S2</t>
   </si>
 </sst>
 </file>
@@ -604,17 +619,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>7</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -642,19 +657,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -682,19 +697,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -722,19 +737,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -762,19 +777,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -802,22 +817,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -844,22 +859,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -886,22 +901,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -928,22 +943,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -970,19 +985,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" s="1" t="s">
+      <c r="F11" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>9</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1010,19 +1025,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1050,19 +1065,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1090,22 +1105,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="1" t="s">
+      <c r="F14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -1132,21 +1147,23 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>45</v>
+      <c r="F15" s="1" t="s">
+        <v>8</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>46</v>
+      <c r="G15" s="1" t="s">
+        <v>66</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
@@ -1172,19 +1189,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1212,19 +1229,19 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1252,22 +1269,22 @@
         <v>15</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -1294,20 +1311,20 @@
         <v>16</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -1334,15 +1351,17 @@
         <v>17</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
-      <c r="G20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -1368,19 +1387,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1408,13 +1427,23 @@
         <v>19</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
+      <c r="C22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -1440,21 +1469,23 @@
         <v>20</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
-      <c r="G23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>69</v>
+      </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
